--- a/artfynd/A 11565-2024 artfynd.xlsx
+++ b/artfynd/A 11565-2024 artfynd.xlsx
@@ -2573,12 +2573,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Josefin Stagnell</t>
+          <t>Josefin Hagernäs</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Josefin Stagnell</t>
+          <t>Josefin Hagernäs</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>

--- a/artfynd/A 11565-2024 artfynd.xlsx
+++ b/artfynd/A 11565-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3427,6 +3427,352 @@
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>125585575</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57632</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Löta gärde, Löta gärde, Srm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>619356</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6568484</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>23:44</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>23:44</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>125585895</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57632</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Löta gärde, Löta gärde, Srm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>619343</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6568505</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>125586866</v>
+      </c>
+      <c r="B26" t="n">
+        <v>95873</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Ålpussen, Ålpussen, Srm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>619596</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6568480</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>02:54</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>02:54</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11565-2024 artfynd.xlsx
+++ b/artfynd/A 11565-2024 artfynd.xlsx
@@ -3546,10 +3546,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125585895</v>
+        <v>125586866</v>
       </c>
       <c r="B25" t="n">
-        <v>57632</v>
+        <v>95873</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3558,43 +3558,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Löta gärde, Löta gärde, Srm</t>
+          <t>Ålpussen, Ålpussen, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>619343</v>
+        <v>619596</v>
       </c>
       <c r="R25" t="n">
-        <v>6568505</v>
+        <v>6568480</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3626,7 +3621,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>02:54</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3636,7 +3631,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>02:54</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3663,10 +3658,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125586866</v>
+        <v>125585895</v>
       </c>
       <c r="B26" t="n">
-        <v>95873</v>
+        <v>57632</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3675,38 +3670,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ålpussen, Ålpussen, Srm</t>
+          <t>Löta gärde, Löta gärde, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>619596</v>
+        <v>619343</v>
       </c>
       <c r="R26" t="n">
-        <v>6568480</v>
+        <v>6568505</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>02:54</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>02:54</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 11565-2024 artfynd.xlsx
+++ b/artfynd/A 11565-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3432,12 +3432,7 @@
         <v>125585575</v>
       </c>
       <c r="B24" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3546,50 +3541,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125586866</v>
+        <v>125585895</v>
       </c>
       <c r="B25" t="n">
-        <v>95873</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ålpussen, Ålpussen, Srm</t>
+          <t>Löta gärde, Löta gärde, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>619596</v>
+        <v>619343</v>
       </c>
       <c r="R25" t="n">
-        <v>6568480</v>
+        <v>6568505</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3621,7 +3616,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>02:54</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3631,7 +3626,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>02:54</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3658,55 +3653,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125585895</v>
+        <v>125586866</v>
       </c>
       <c r="B26" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95927</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Löta gärde, Löta gärde, Srm</t>
+          <t>Ålpussen, Ålpussen, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>619343</v>
+        <v>619596</v>
       </c>
       <c r="R26" t="n">
-        <v>6568505</v>
+        <v>6568480</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3738,7 +3723,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>02:54</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3748,7 +3733,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>02:54</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3772,6 +3757,126 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>125787306</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57453</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>102118</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Nattskärra</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Caprimulgus europaeus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lundby skog, Lundby skog, Srm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>619349</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6568288</v>
+      </c>
+      <c r="S27" t="n">
+        <v>20</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>01:47</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>01:47</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11565-2024 artfynd.xlsx
+++ b/artfynd/A 11565-2024 artfynd.xlsx
@@ -3656,7 +3656,7 @@
         <v>125586866</v>
       </c>
       <c r="B26" t="n">
-        <v>95927</v>
+        <v>95934</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 11565-2024 artfynd.xlsx
+++ b/artfynd/A 11565-2024 artfynd.xlsx
@@ -3656,7 +3656,7 @@
         <v>125586866</v>
       </c>
       <c r="B26" t="n">
-        <v>95934</v>
+        <v>95937</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 11565-2024 artfynd.xlsx
+++ b/artfynd/A 11565-2024 artfynd.xlsx
@@ -3656,7 +3656,7 @@
         <v>125586866</v>
       </c>
       <c r="B26" t="n">
-        <v>95937</v>
+        <v>95941</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 11565-2024 artfynd.xlsx
+++ b/artfynd/A 11565-2024 artfynd.xlsx
@@ -3656,7 +3656,7 @@
         <v>125586866</v>
       </c>
       <c r="B26" t="n">
-        <v>95941</v>
+        <v>95942</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 11565-2024 artfynd.xlsx
+++ b/artfynd/A 11565-2024 artfynd.xlsx
@@ -3432,7 +3432,7 @@
         <v>125585575</v>
       </c>
       <c r="B24" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>125585895</v>
       </c>
       <c r="B25" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>125586866</v>
       </c>
       <c r="B26" t="n">
-        <v>95942</v>
+        <v>95944</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>125787306</v>
       </c>
       <c r="B27" t="n">
-        <v>57453</v>
+        <v>57454</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 11565-2024 artfynd.xlsx
+++ b/artfynd/A 11565-2024 artfynd.xlsx
@@ -3656,7 +3656,7 @@
         <v>125586866</v>
       </c>
       <c r="B26" t="n">
-        <v>95944</v>
+        <v>95946</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 11565-2024 artfynd.xlsx
+++ b/artfynd/A 11565-2024 artfynd.xlsx
@@ -3656,7 +3656,7 @@
         <v>125586866</v>
       </c>
       <c r="B26" t="n">
-        <v>95946</v>
+        <v>95948</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 11565-2024 artfynd.xlsx
+++ b/artfynd/A 11565-2024 artfynd.xlsx
@@ -3763,7 +3763,7 @@
         <v>125787306</v>
       </c>
       <c r="B27" t="n">
-        <v>57454</v>
+        <v>57458</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 11565-2024 artfynd.xlsx
+++ b/artfynd/A 11565-2024 artfynd.xlsx
@@ -3763,7 +3763,7 @@
         <v>125787306</v>
       </c>
       <c r="B27" t="n">
-        <v>57458</v>
+        <v>57459</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
